--- a/research/traditional_assets/database/data/mauritius/mauritius_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2526</v>
+        <v>0.307</v>
       </c>
       <c r="E2">
-        <v>0.1945</v>
+        <v>0.182</v>
       </c>
       <c r="G2">
-        <v>0.07103372028745165</v>
+        <v>0.07055837563451776</v>
       </c>
       <c r="H2">
-        <v>0.07103372028745165</v>
+        <v>0.07055837563451776</v>
       </c>
       <c r="I2">
-        <v>0.05655058043117746</v>
+        <v>0.05421319796954314</v>
       </c>
       <c r="J2">
-        <v>0.05088417701316428</v>
+        <v>0.04612153873060625</v>
       </c>
       <c r="K2">
-        <v>22.63</v>
+        <v>21.38</v>
       </c>
       <c r="L2">
-        <v>0.06254836926478718</v>
+        <v>0.05426395939086295</v>
       </c>
       <c r="M2">
-        <v>5.96</v>
+        <v>5.84</v>
       </c>
       <c r="N2">
-        <v>0.02464846980976013</v>
+        <v>0.02607142857142857</v>
       </c>
       <c r="O2">
-        <v>0.2633672116659301</v>
+        <v>0.2731524789522918</v>
       </c>
       <c r="P2">
-        <v>5.96</v>
+        <v>5.84</v>
       </c>
       <c r="Q2">
-        <v>0.02464846980976013</v>
+        <v>0.02607142857142857</v>
       </c>
       <c r="R2">
-        <v>0.2633672116659301</v>
+        <v>0.2731524789522918</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>139.5</v>
+        <v>104.8</v>
       </c>
       <c r="V2">
-        <v>0.5769230769230769</v>
+        <v>0.4678571428571429</v>
       </c>
       <c r="W2">
-        <v>0.1361910526441333</v>
+        <v>0.1059790032676347</v>
       </c>
       <c r="X2">
-        <v>0.05948019837534929</v>
+        <v>0.1014230805956945</v>
       </c>
       <c r="Y2">
-        <v>0.07671085426878399</v>
+        <v>0.004555922671940202</v>
       </c>
       <c r="Z2">
-        <v>5.266375545851528</v>
-      </c>
-      <c r="AA2">
-        <v>-0.4052299139061708</v>
+        <v>4.581395348837209</v>
       </c>
       <c r="AB2">
-        <v>0.05798293541183604</v>
-      </c>
-      <c r="AC2">
-        <v>-0.4632128493180068</v>
+        <v>0.09907573846581652</v>
       </c>
       <c r="AD2">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="AG2">
-        <v>-120.4</v>
+        <v>-86.8</v>
       </c>
       <c r="AH2">
-        <v>0.07320812571866615</v>
+        <v>0.0743801652892562</v>
       </c>
       <c r="AI2">
-        <v>0.07726537216828479</v>
+        <v>0.07182761372705507</v>
       </c>
       <c r="AJ2">
-        <v>-0.9917627677100495</v>
+        <v>-0.6326530612244898</v>
       </c>
       <c r="AK2">
-        <v>-1.117920148560817</v>
+        <v>-0.5953360768175582</v>
       </c>
       <c r="AL2">
-        <v>0.955</v>
+        <v>0.624</v>
       </c>
       <c r="AM2">
-        <v>0.955</v>
+        <v>0.624</v>
       </c>
       <c r="AN2">
-        <v>0.7958333333333334</v>
+        <v>0.7531380753138076</v>
       </c>
       <c r="AO2">
-        <v>21.42408376963351</v>
+        <v>34.23076923076923</v>
       </c>
       <c r="AP2">
-        <v>-5.016666666666667</v>
+        <v>-3.631799163179916</v>
       </c>
       <c r="AQ2">
-        <v>21.42408376963351</v>
+        <v>34.23076923076923</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MUA Ltd (MUSE:MUAL.N0000)</t>
+          <t>Swan General Ltd (MUSE:SWAN.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +716,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0992</v>
+        <v>0.465</v>
       </c>
       <c r="E3">
-        <v>0.187</v>
+        <v>0.249</v>
       </c>
       <c r="G3">
-        <v>0.1103117505995204</v>
+        <v>0.06325301204819277</v>
       </c>
       <c r="H3">
-        <v>0.1103117505995204</v>
+        <v>0.06325301204819277</v>
       </c>
       <c r="I3">
-        <v>0.09592326139088729</v>
+        <v>0.05421686746987951</v>
       </c>
       <c r="J3">
-        <v>0.08174699178710129</v>
+        <v>0.05041073384446878</v>
       </c>
       <c r="K3">
-        <v>9.130000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="L3">
-        <v>0.07298161470823342</v>
+        <v>0.06368330464716007</v>
       </c>
       <c r="M3">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="N3">
-        <v>0.0199874686716792</v>
+        <v>0.0314769975786925</v>
       </c>
       <c r="O3">
-        <v>0.3493975903614457</v>
+        <v>0.1756756756756757</v>
       </c>
       <c r="P3">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="Q3">
-        <v>0.0199874686716792</v>
+        <v>0.0314769975786925</v>
       </c>
       <c r="R3">
-        <v>0.3493975903614457</v>
+        <v>0.1756756756756757</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>23.9</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.149749373433584</v>
+        <v>1.030266343825666</v>
       </c>
       <c r="W3">
-        <v>0.1230458221024259</v>
+        <v>0.1394910461828464</v>
       </c>
       <c r="X3">
-        <v>0.06162819283217042</v>
+        <v>0.09820894730782419</v>
       </c>
       <c r="Y3">
-        <v>0.06141762927025547</v>
-      </c>
-      <c r="Z3">
-        <v>1.620466321243524</v>
-      </c>
-      <c r="AA3">
-        <v>0.1324682470539686</v>
+        <v>0.0412820988750222</v>
       </c>
       <c r="AB3">
-        <v>0.05863366690514392</v>
-      </c>
-      <c r="AC3">
-        <v>0.07383458014882464</v>
+        <v>0.09820894730782419</v>
       </c>
       <c r="AD3">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4.799999999999997</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1068830442081701</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.14921875</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03100775193798447</v>
+        <v>34.04</v>
       </c>
       <c r="AK3">
-        <v>-0.0461095100864553</v>
+        <v>-2.827242524916942</v>
       </c>
       <c r="AL3">
-        <v>0.855</v>
+        <v>0.031</v>
       </c>
       <c r="AM3">
-        <v>0.855</v>
+        <v>0.031</v>
       </c>
       <c r="AN3">
-        <v>1.394160583941606</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>14.03508771929825</v>
+        <v>406.4516129032258</v>
       </c>
       <c r="AP3">
-        <v>-0.3503649635036494</v>
+        <v>-6.303703703703703</v>
       </c>
       <c r="AQ3">
-        <v>14.03508771929825</v>
+        <v>406.4516129032258</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Swan General Ltd (MUSE:SWAN.N0000)</t>
+          <t>MUA Ltd (MUSE:MUAL.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +841,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.406</v>
+        <v>0.149</v>
       </c>
       <c r="E4">
-        <v>0.202</v>
+        <v>0.115</v>
       </c>
       <c r="G4">
-        <v>0.05027460920997043</v>
+        <v>0.08106435643564357</v>
       </c>
       <c r="H4">
-        <v>0.05027460920997043</v>
+        <v>0.08106435643564357</v>
       </c>
       <c r="I4">
-        <v>0.03574144486692016</v>
+        <v>0.05420792079207921</v>
       </c>
       <c r="J4">
-        <v>0.03386095748358106</v>
+        <v>0.04183168316831683</v>
       </c>
       <c r="K4">
-        <v>13.5</v>
+        <v>6.58</v>
       </c>
       <c r="L4">
-        <v>0.05703422053231939</v>
+        <v>0.04071782178217822</v>
       </c>
       <c r="M4">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="N4">
-        <v>0.03369829683698296</v>
+        <v>0.02291371994342292</v>
       </c>
       <c r="O4">
-        <v>0.2051851851851852</v>
+        <v>0.4924012158054711</v>
       </c>
       <c r="P4">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="Q4">
-        <v>0.03369829683698296</v>
+        <v>0.02291371994342292</v>
       </c>
       <c r="R4">
-        <v>0.2051851851851852</v>
+        <v>0.4924012158054711</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +889,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>115.6</v>
+        <v>19.7</v>
       </c>
       <c r="V4">
-        <v>1.40632603406326</v>
+        <v>0.1393210749646393</v>
       </c>
       <c r="W4">
-        <v>0.1493362831858407</v>
+        <v>0.07246696035242291</v>
       </c>
       <c r="X4">
-        <v>0.05733220391852815</v>
+        <v>0.1046372138835647</v>
       </c>
       <c r="Y4">
-        <v>0.09200407926731254</v>
+        <v>-0.03217025353114181</v>
       </c>
       <c r="Z4">
-        <v>-27.84705882352941</v>
+        <v>1.87906976744186</v>
       </c>
       <c r="AA4">
-        <v>-0.9429280748663101</v>
+        <v>0.0786046511627907</v>
       </c>
       <c r="AB4">
-        <v>0.05733220391852815</v>
+        <v>0.09994252962380885</v>
       </c>
       <c r="AC4">
-        <v>-1.000260278784838</v>
+        <v>-0.02133787846101816</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG4">
-        <v>-115.6</v>
+        <v>-1.699999999999999</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.1129234629861982</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.1329394387001477</v>
       </c>
       <c r="AJ4">
-        <v>3.461077844311378</v>
+        <v>-0.01216893342877594</v>
       </c>
       <c r="AK4">
-        <v>-32.11111111111104</v>
+        <v>-0.01469317199654278</v>
       </c>
       <c r="AL4">
-        <v>0.1</v>
+        <v>0.593</v>
       </c>
       <c r="AM4">
-        <v>0.1</v>
+        <v>0.593</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="AO4">
-        <v>84.60000000000001</v>
+        <v>14.77234401349073</v>
       </c>
       <c r="AP4">
-        <v>-11.22330097087378</v>
+        <v>-0.1634615384615384</v>
       </c>
       <c r="AQ4">
-        <v>84.60000000000001</v>
+        <v>14.77234401349073</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mauritius/mauritius_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.307</v>
+        <v>0.23195</v>
       </c>
       <c r="E2">
-        <v>0.182</v>
+        <v>0.07835</v>
       </c>
       <c r="G2">
-        <v>0.07055837563451776</v>
+        <v>0.07679263565891474</v>
       </c>
       <c r="H2">
-        <v>0.07055837563451776</v>
+        <v>0.07679263565891474</v>
       </c>
       <c r="I2">
-        <v>0.05421319796954314</v>
+        <v>0.06734496124031007</v>
       </c>
       <c r="J2">
-        <v>0.04612153873060625</v>
+        <v>0.05744402980505735</v>
       </c>
       <c r="K2">
-        <v>21.38</v>
+        <v>21.75</v>
       </c>
       <c r="L2">
-        <v>0.05426395939086295</v>
+        <v>0.05268895348837209</v>
       </c>
       <c r="M2">
-        <v>5.84</v>
+        <v>6.31</v>
       </c>
       <c r="N2">
-        <v>0.02607142857142857</v>
+        <v>0.03048309178743962</v>
       </c>
       <c r="O2">
-        <v>0.2731524789522918</v>
+        <v>0.2901149425287357</v>
       </c>
       <c r="P2">
-        <v>5.84</v>
+        <v>6.31</v>
       </c>
       <c r="Q2">
-        <v>0.02607142857142857</v>
+        <v>0.03048309178743962</v>
       </c>
       <c r="R2">
-        <v>0.2731524789522918</v>
+        <v>0.2901149425287357</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>104.8</v>
+        <v>123.4</v>
       </c>
       <c r="V2">
-        <v>0.4678571428571429</v>
+        <v>0.5961352657004831</v>
       </c>
       <c r="W2">
-        <v>0.1059790032676347</v>
+        <v>0.1085397105047148</v>
       </c>
       <c r="X2">
-        <v>0.1014230805956945</v>
+        <v>0.0915737990901446</v>
       </c>
       <c r="Y2">
-        <v>0.004555922671940202</v>
+        <v>0.01696591141457021</v>
       </c>
       <c r="Z2">
-        <v>4.581395348837209</v>
+        <v>3.649867374005305</v>
+      </c>
+      <c r="AA2">
+        <v>0.5986098213446838</v>
       </c>
       <c r="AB2">
-        <v>0.09907573846581652</v>
+        <v>0.08908740400593949</v>
+      </c>
+      <c r="AC2">
+        <v>0.5095224173387443</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="AG2">
-        <v>-86.8</v>
+        <v>-98.80000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0743801652892562</v>
+        <v>0.1062176165803109</v>
       </c>
       <c r="AI2">
-        <v>0.07182761372705507</v>
+        <v>0.0877005347593583</v>
       </c>
       <c r="AJ2">
-        <v>-0.6326530612244898</v>
+        <v>-0.9131238447319781</v>
       </c>
       <c r="AK2">
-        <v>-0.5953360768175582</v>
+        <v>-0.628898790579249</v>
       </c>
       <c r="AL2">
-        <v>0.624</v>
+        <v>0.8380000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.624</v>
+        <v>0.8380000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.7531380753138076</v>
+        <v>0.8172757475083057</v>
       </c>
       <c r="AO2">
-        <v>34.23076923076923</v>
+        <v>33.17422434367541</v>
       </c>
       <c r="AP2">
-        <v>-3.631799163179916</v>
+        <v>-3.282392026578073</v>
       </c>
       <c r="AQ2">
-        <v>34.23076923076923</v>
+        <v>33.17422434367541</v>
       </c>
     </row>
     <row r="3">
@@ -716,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.465</v>
+        <v>0.401</v>
       </c>
       <c r="E3">
-        <v>0.249</v>
+        <v>0.213</v>
       </c>
       <c r="G3">
-        <v>0.06325301204819277</v>
+        <v>0.07341772151898734</v>
       </c>
       <c r="H3">
-        <v>0.06325301204819277</v>
+        <v>0.07341772151898734</v>
       </c>
       <c r="I3">
-        <v>0.05421686746987951</v>
+        <v>0.06690777576853527</v>
       </c>
       <c r="J3">
-        <v>0.05041073384446878</v>
+        <v>0.06215948200431664</v>
       </c>
       <c r="K3">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="L3">
-        <v>0.06368330464716007</v>
+        <v>0.06075949367088608</v>
       </c>
       <c r="M3">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="N3">
-        <v>0.0314769975786925</v>
+        <v>0.03194278903456496</v>
       </c>
       <c r="O3">
-        <v>0.1756756756756757</v>
+        <v>0.1595238095238095</v>
       </c>
       <c r="P3">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="Q3">
-        <v>0.0314769975786925</v>
+        <v>0.03194278903456496</v>
       </c>
       <c r="R3">
-        <v>0.1756756756756757</v>
+        <v>0.1595238095238095</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,22 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>85.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="V3">
-        <v>1.030266343825666</v>
+        <v>1.144219308700834</v>
       </c>
       <c r="W3">
-        <v>0.1394910461828464</v>
+        <v>0.1673306772908366</v>
       </c>
       <c r="X3">
-        <v>0.09820894730782419</v>
+        <v>0.08744254178425967</v>
       </c>
       <c r="Y3">
-        <v>0.0412820988750222</v>
+        <v>0.07988813550657697</v>
+      </c>
+      <c r="Z3">
+        <v>18.07189542483659</v>
+      </c>
+      <c r="AA3">
+        <v>1.123339658444022</v>
       </c>
       <c r="AB3">
-        <v>0.09820894730782419</v>
+        <v>0.08744254178425967</v>
+      </c>
+      <c r="AC3">
+        <v>1.035897116659762</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-85.09999999999999</v>
+        <v>-96</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>34.04</v>
+        <v>7.933884297520665</v>
       </c>
       <c r="AK3">
-        <v>-2.827242524916942</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="AL3">
-        <v>0.031</v>
+        <v>0.05</v>
       </c>
       <c r="AM3">
-        <v>0.031</v>
+        <v>0.05</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>406.4516129032258</v>
+        <v>370</v>
       </c>
       <c r="AP3">
-        <v>-6.303703703703703</v>
+        <v>-4.873096446700508</v>
       </c>
       <c r="AQ3">
-        <v>406.4516129032258</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
@@ -841,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.149</v>
+        <v>0.0629</v>
       </c>
       <c r="E4">
-        <v>0.115</v>
+        <v>-0.0563</v>
       </c>
       <c r="G4">
-        <v>0.08106435643564357</v>
+        <v>0.08363903154805576</v>
       </c>
       <c r="H4">
-        <v>0.08106435643564357</v>
+        <v>0.08363903154805576</v>
       </c>
       <c r="I4">
-        <v>0.05420792079207921</v>
+        <v>0.06823184152604549</v>
       </c>
       <c r="J4">
-        <v>0.04183168316831683</v>
+        <v>0.05301146338367408</v>
       </c>
       <c r="K4">
-        <v>6.58</v>
+        <v>4.95</v>
       </c>
       <c r="L4">
-        <v>0.04071782178217822</v>
+        <v>0.03631694790902421</v>
       </c>
       <c r="M4">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="N4">
-        <v>0.02291371994342292</v>
+        <v>0.02948822095857027</v>
       </c>
       <c r="O4">
-        <v>0.4924012158054711</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P4">
-        <v>3.24</v>
+        <v>3.63</v>
       </c>
       <c r="Q4">
-        <v>0.02291371994342292</v>
+        <v>0.02948822095857027</v>
       </c>
       <c r="R4">
-        <v>0.4924012158054711</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>19.7</v>
+        <v>27.4</v>
       </c>
       <c r="V4">
-        <v>0.1393210749646393</v>
+        <v>0.2225832656376929</v>
       </c>
       <c r="W4">
-        <v>0.07246696035242291</v>
+        <v>0.04974874371859297</v>
       </c>
       <c r="X4">
-        <v>0.1046372138835647</v>
+        <v>0.09570505639602954</v>
       </c>
       <c r="Y4">
-        <v>-0.03217025353114181</v>
+        <v>-0.04595631267743657</v>
       </c>
       <c r="Z4">
-        <v>1.87906976744186</v>
+        <v>1.393660531697342</v>
       </c>
       <c r="AA4">
-        <v>0.0786046511627907</v>
+        <v>0.07387998424534538</v>
       </c>
       <c r="AB4">
-        <v>0.09994252962380885</v>
+        <v>0.09073226622761932</v>
       </c>
       <c r="AC4">
-        <v>-0.02133787846101816</v>
+        <v>-0.01685228198227394</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="AG4">
-        <v>-1.699999999999999</v>
+        <v>-2.799999999999997</v>
       </c>
       <c r="AH4">
-        <v>0.1129234629861982</v>
+        <v>0.1665538253215978</v>
       </c>
       <c r="AI4">
-        <v>0.1329394387001477</v>
+        <v>0.1726315789473684</v>
       </c>
       <c r="AJ4">
-        <v>-0.01216893342877594</v>
+        <v>-0.02327514546965916</v>
       </c>
       <c r="AK4">
-        <v>-0.01469317199654278</v>
+        <v>-0.02432667245873151</v>
       </c>
       <c r="AL4">
-        <v>0.593</v>
+        <v>0.788</v>
       </c>
       <c r="AM4">
-        <v>0.593</v>
+        <v>0.788</v>
       </c>
       <c r="AN4">
-        <v>1.730769230769231</v>
+        <v>2.365384615384615</v>
       </c>
       <c r="AO4">
-        <v>14.77234401349073</v>
+        <v>11.80203045685279</v>
       </c>
       <c r="AP4">
-        <v>-0.1634615384615384</v>
+        <v>-0.2692307692307689</v>
       </c>
       <c r="AQ4">
-        <v>14.77234401349073</v>
+        <v>11.80203045685279</v>
       </c>
     </row>
   </sheetData>
